--- a/气象/表格文件/全国所有站点(国家站)全年及各月极端高低温.xlsx
+++ b/气象/表格文件/全国所有站点(国家站)全年及各月极端高低温.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB3DA6A-746F-4212-8EFC-F73C8CEA9D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C482A51-635C-40AC-98E8-102C565F9C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{172DB64A-34A6-4C2C-B594-936105A71AD1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{172DB64A-34A6-4C2C-B594-936105A71AD1}"/>
   </bookViews>
   <sheets>
     <sheet name="国家站极端温度" sheetId="1" r:id="rId1"/>
     <sheet name="各省最低温" sheetId="2" r:id="rId2"/>
+    <sheet name="各省最低一均" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">国家站极端温度!$A$1:$H$2470</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7561" uniqueCount="2511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7832" uniqueCount="2685">
   <si>
     <t>黑龙江</t>
   </si>
@@ -7492,25 +7493,6 @@
     <t>珊瑚</t>
   </si>
   <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>北极村</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1997之前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2002之后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>新疆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7523,10 +7505,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>劲涛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>内蒙古</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7535,14 +7513,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>蒙兀室韦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠河</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>台湾</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7551,10 +7521,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大潭山</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>澳门</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7567,26 +7533,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>各省历史最低气温</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>来源网络</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可可托海</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非定居点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60年代老站址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>最低气温(℃)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7599,15 +7545,834 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>站点/地点</t>
+    <t>⏱️</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>特尼河试验站</t>
+    <t>🌏</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>白山景区下</t>
+    <t>阿木尔镇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东戈壁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂特冈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌布苏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扎布汗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🪪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古国</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各地历史最低气温记录(东亚)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图瓦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>托拉赫姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古国最低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北海道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旭川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日本最低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国内最低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中江镇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朝鲜最低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塞罕坝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐家汇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1893-01-19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天目山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宿迁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杨平郡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩国最低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔泰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>科什阿加奇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布里亚特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗曼诺夫卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>米努辛斯克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉斯诺
+亚尔斯克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊尔库茨克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bayanday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈巴罗夫
+斯克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索菲斯克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿穆尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VERHNJAJA TOM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外贝加尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌留皮诺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气候周期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最冷月均温(℃)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埃尔津</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1991-2020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最冷月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一月</t>
+  </si>
+  <si>
+    <t>1991-2020</t>
+  </si>
+  <si>
+    <t>纬度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海拔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1759m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各地最冷站(东亚+定居点)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埃基姆昌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>540m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>997m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3191人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1212人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2792人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7900人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2156m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2576人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戈尔必齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>384m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴尔古津</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>488m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5702人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切昆达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>271m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>166人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库苏古尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁钦隆勃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1582m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4262人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡丘格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>533m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1356人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三池渊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1381m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31471人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>321906人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>116m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>284855人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.1m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>678800人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7413070人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1991-2019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>301m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>181100人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>433m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29614人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>689m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5493人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴音布鲁克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2458m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8249人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1991-2020
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>推测</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1997</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2020</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2000</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2020</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特泥河试验站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>托勒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3367m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>39683人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛟河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>392000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右玉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1346m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>295m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85797人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西丰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>196m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>205000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1961-2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1507m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>667人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石渠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4200m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100600人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1770m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马鬃山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>671人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兴仁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1698m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30915人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>332m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9164人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>941m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神木</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汤河口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>584100人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐陵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>538200人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝坻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>710100人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香格里拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3342m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>186400人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>798m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>196500人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>砀山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>44m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>763000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>367m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林州</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>927400人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赣榆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>991900人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长兴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>688000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>935m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>77058人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神农架林区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>385900人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞昌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹子湖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>607m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100+人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临湘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>424100人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寿宁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>845m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>171000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1722m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>650300人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崇明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>663500人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>408m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>138000人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95700人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西林吉镇(漠河)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1991-2020</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+推测</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7615,12 +8380,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="180" formatCode="0_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7655,7 +8421,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
@@ -7663,7 +8430,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
@@ -7672,7 +8467,7 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="24"/>
       <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
@@ -7681,8 +8476,17 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color rgb="FFFFFF3F"/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FFFFFF00"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -7691,7 +8495,21 @@
     <font>
       <b/>
       <sz val="20"/>
-      <color rgb="FF000000"/>
+      <color theme="0"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -7699,59 +8517,15 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="0" tint="-0.249977111117893"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFFFF00"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FF00B0F0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFFC000"/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="31">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7766,127 +8540,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3218D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD1F8F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD61E92"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF1D94"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC91B97"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC21A99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC189C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB5179E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAE16A1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA814A3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8D0FAD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF800CB2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF670AB3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF610AB1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4E0CAA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF480CA8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF450CA7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF420CA6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3B15AB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3C1DB2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3D26BA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7904,36 +8564,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4576EE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4680EF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF4895EF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4BBFF0"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8FD6E4"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF72585"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7209B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF560BAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3A0CA3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CC9F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -7958,8 +8660,47 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color theme="0"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color theme="0"/>
@@ -7982,68 +8723,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="0"/>
-      </top>
-      <bottom style="medium">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8071,143 +8757,170 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    <xf numFmtId="178" fontId="5" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    <xf numFmtId="178" fontId="5" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="20" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="22" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="23" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="24" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="26" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="27" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="28" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="29" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="30" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="178" fontId="15" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="178" fontId="15" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8215,6 +8928,20 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF4CC9F0"/>
+      <color rgb="FF4895EF"/>
+      <color rgb="FF4361EE"/>
+      <color rgb="FF3F37C9"/>
+      <color rgb="FF3A0CA3"/>
+      <color rgb="FF480CA8"/>
+      <color rgb="FF560BAD"/>
+      <color rgb="FF7209B7"/>
+      <color rgb="FFB5179E"/>
+      <color rgb="FFF72585"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -80174,1040 +80901,2137 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F8CD8AC-0906-4D8B-9742-1E6BA5AF7DE6}">
-  <dimension ref="A1:E67"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="28.59765625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="28.59765625" style="9" customWidth="1"/>
     <col min="3" max="3" width="28.59765625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.59765625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="18.59765625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.59765625" style="9" customWidth="1"/>
     <col min="6" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="41" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="43" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="35" t="s">
+        <v>2491</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="30" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>2505</v>
+      </c>
+      <c r="C3" s="32">
+        <v>-57.3</v>
+      </c>
+      <c r="D3" s="33">
+        <v>25203</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="28" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C4" s="16">
+        <v>-56.3</v>
+      </c>
+      <c r="D4" s="26">
+        <v>28866</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="28" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C5" s="16">
+        <v>-55.6</v>
+      </c>
+      <c r="D5" s="26">
+        <v>24467</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="28" t="s">
         <v>2500</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-    </row>
-    <row r="2" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="49" t="s">
+      <c r="B6" s="14" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C6" s="16">
+        <v>-55.3</v>
+      </c>
+      <c r="D6" s="26">
+        <v>42397</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="28" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C7" s="16">
+        <v>-55.1</v>
+      </c>
+      <c r="D7" s="26">
+        <v>14639</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="28" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C8" s="16">
+        <v>-55</v>
+      </c>
+      <c r="D8" s="26">
+        <v>44948</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="28" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>2524</v>
+      </c>
+      <c r="C9" s="17">
+        <v>-54.5</v>
+      </c>
+      <c r="D9" s="26">
+        <v>20474</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="29" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C10" s="17">
+        <v>-53.9</v>
+      </c>
+      <c r="D10" s="26">
+        <v>19349</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="12" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C11" s="17">
+        <v>-53</v>
+      </c>
+      <c r="D11" s="26">
+        <v>44948</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="12" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C12" s="17">
+        <v>-52.4</v>
+      </c>
+      <c r="D12" s="26">
+        <v>44948</v>
+      </c>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="12" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>2482</v>
+      </c>
+      <c r="C13" s="17">
+        <v>-52.3</v>
+      </c>
+      <c r="D13" s="26">
+        <v>45340</v>
+      </c>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="29" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>2525</v>
+      </c>
+      <c r="C14" s="17">
+        <v>-52.2</v>
+      </c>
+      <c r="D14" s="26">
+        <v>11331</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C15" s="17">
+        <v>-51.7</v>
+      </c>
+      <c r="D15" s="26">
+        <v>5491</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="12" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>2493</v>
+      </c>
+      <c r="C16" s="18">
+        <v>-49.7</v>
+      </c>
+      <c r="D16" s="26">
+        <v>42014</v>
+      </c>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="C17" s="18">
+        <v>-46.4</v>
+      </c>
+      <c r="D17" s="26">
+        <v>24114</v>
+      </c>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="18">
+        <v>-45</v>
+      </c>
+      <c r="D18" s="26">
+        <v>25572</v>
+      </c>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="C19" s="19">
+        <v>-44.8</v>
+      </c>
+      <c r="D19" s="26">
+        <v>21200</v>
+      </c>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="14" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C20" s="19">
+        <v>-43.6</v>
+      </c>
+      <c r="D20" s="26">
+        <v>12066</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="C21" s="19">
+        <v>-43.4</v>
+      </c>
+      <c r="D21" s="26">
+        <v>36904</v>
+      </c>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C22" s="19">
+        <v>-43.3</v>
+      </c>
+      <c r="D22" s="26">
+        <v>40183</v>
+      </c>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
         <v>2508</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="47" t="s">
-        <v>2505</v>
-      </c>
-      <c r="D2" s="47" t="s">
+      <c r="B23" s="14" t="s">
+        <v>2509</v>
+      </c>
+      <c r="C23" s="19">
+        <v>-41</v>
+      </c>
+      <c r="D23" s="26">
+        <v>756</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="12" t="s">
+        <v>782</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="C24" s="20">
+        <v>-37.799999999999997</v>
+      </c>
+      <c r="D24" s="26">
+        <v>35062</v>
+      </c>
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C25" s="20">
+        <v>-37.1</v>
+      </c>
+      <c r="D25" s="26">
+        <v>37615</v>
+      </c>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C26" s="20">
+        <v>-33.200000000000003</v>
+      </c>
+      <c r="D26" s="26">
+        <v>24816</v>
+      </c>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C27" s="20">
+        <v>-33.200000000000003</v>
+      </c>
+      <c r="D27" s="26">
+        <v>29250</v>
+      </c>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C28" s="20">
+        <v>-32.700000000000003</v>
+      </c>
+      <c r="D28" s="26">
+        <v>20086</v>
+      </c>
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28"/>
+      <c r="B29" s="14" t="s">
+        <v>2519</v>
+      </c>
+      <c r="C29" s="20">
+        <v>-32.6</v>
+      </c>
+      <c r="D29" s="26">
+        <v>29591</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="12" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C30" s="21">
+        <v>-27.5</v>
+      </c>
+      <c r="D30" s="26">
+        <v>21200</v>
+      </c>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="12" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C31" s="21">
+        <v>-27.4</v>
+      </c>
+      <c r="D31" s="26">
+        <v>24160</v>
+      </c>
+      <c r="E31" s="11"/>
+    </row>
+    <row r="32" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C32" s="21">
+        <v>-27.4</v>
+      </c>
+      <c r="D32" s="26">
+        <v>30312</v>
+      </c>
+      <c r="E32" s="11"/>
+    </row>
+    <row r="33" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="12" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C33" s="21">
+        <v>-25.8</v>
+      </c>
+      <c r="D33" s="26">
+        <v>20813</v>
+      </c>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="34" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="12" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C34" s="22">
+        <v>-24.3</v>
+      </c>
+      <c r="D34" s="26">
+        <v>25240</v>
+      </c>
+      <c r="E34" s="11"/>
+    </row>
+    <row r="35" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C35" s="22">
+        <v>-23.6</v>
+      </c>
+      <c r="D35" s="26">
+        <v>28120</v>
+      </c>
+      <c r="E35" s="11"/>
+    </row>
+    <row r="36" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="12" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C36" s="22">
+        <v>-23.4</v>
+      </c>
+      <c r="D36" s="26">
+        <v>25239</v>
+      </c>
+      <c r="E36" s="11"/>
+    </row>
+    <row r="37" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="12" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>2517</v>
+      </c>
+      <c r="C37" s="22">
+        <v>-20.6</v>
+      </c>
+      <c r="D37" s="26">
+        <v>21201</v>
+      </c>
+      <c r="E37" s="11"/>
+    </row>
+    <row r="38" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="12" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C38" s="23">
+        <v>-19.7</v>
+      </c>
+      <c r="D38" s="26">
+        <v>28155</v>
+      </c>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C39" s="23">
+        <v>-18.899999999999999</v>
+      </c>
+      <c r="D39" s="26">
+        <v>25240</v>
+      </c>
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="12" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>2487</v>
+      </c>
+      <c r="C40" s="23">
+        <v>-18.399999999999999</v>
+      </c>
+      <c r="D40" s="26">
+        <v>25599</v>
+      </c>
+      <c r="E40" s="11"/>
+    </row>
+    <row r="41" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="12" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C41" s="23">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="D41" s="26">
+        <v>25234</v>
+      </c>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="42" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="12" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C42" s="23">
+        <v>-15.6</v>
+      </c>
+      <c r="D42" s="26">
+        <v>42394</v>
+      </c>
+      <c r="E42" s="11"/>
+    </row>
+    <row r="43" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="12" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C43" s="23">
+        <v>-15.3</v>
+      </c>
+      <c r="D43" s="26">
+        <v>28165</v>
+      </c>
+      <c r="E43" s="11"/>
+    </row>
+    <row r="44" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="12" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>2515</v>
+      </c>
+      <c r="C44" s="23">
+        <v>-12.1</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>2516</v>
+      </c>
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="12" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C45" s="24">
+        <v>-8.4</v>
+      </c>
+      <c r="D45" s="26">
+        <v>23026</v>
+      </c>
+      <c r="E45" s="11"/>
+    </row>
+    <row r="46" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="12" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C46" s="24">
+        <v>-7.3</v>
+      </c>
+      <c r="D46" s="26">
+        <v>20101</v>
+      </c>
+      <c r="E46" s="11"/>
+    </row>
+    <row r="47" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="12" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>2490</v>
+      </c>
+      <c r="C47" s="24">
+        <v>-6</v>
+      </c>
+      <c r="D47" s="26">
+        <v>42393</v>
+      </c>
+      <c r="E47" s="11"/>
+    </row>
+    <row r="48" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="12"/>
+      <c r="B48" s="10" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C48" s="25">
+        <v>-1.8</v>
+      </c>
+      <c r="D48" s="26">
+        <v>17558</v>
+      </c>
+      <c r="E48" s="11"/>
+    </row>
+    <row r="49" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="12" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C49" s="25">
+        <v>-1.4</v>
+      </c>
+      <c r="D49" s="26">
+        <v>23026</v>
+      </c>
+      <c r="E49" s="11"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E49">
+    <sortCondition ref="C3:C49"/>
+    <sortCondition ref="D3:D49"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6513AEFC-FB9C-4F0A-8F2E-8270FCA49C94}">
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.59765625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="28.59765625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.59765625" style="44" customWidth="1"/>
+    <col min="5" max="5" width="28.59765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.59765625" style="45" customWidth="1"/>
+    <col min="7" max="7" width="10.59765625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="12.59765625" style="45" customWidth="1"/>
+    <col min="9" max="9" width="18.59765625" style="9" customWidth="1"/>
+    <col min="10" max="16384" width="9.06640625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="51" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="53"/>
+    </row>
+    <row r="2" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>2539</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>2543</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>2544</v>
+      </c>
+      <c r="H2" s="50" t="s">
+        <v>2546</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="30" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E3" s="38">
+        <v>-34.200000000000003</v>
+      </c>
+      <c r="F3" s="59">
+        <v>49.905966669999998</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>2551</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>2554</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="28" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E4" s="39">
+        <v>-32.9</v>
+      </c>
+      <c r="F4" s="59">
+        <v>47.209699999999998</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>2556</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>2557</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="29" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E5" s="39">
+        <v>-32.4</v>
+      </c>
+      <c r="F5" s="59">
+        <v>51.1</v>
+      </c>
+      <c r="G5" s="60" t="s">
+        <v>2569</v>
+      </c>
+      <c r="H5" s="62" t="s">
+        <v>2570</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="28" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E6" s="39">
+        <v>-31.5</v>
+      </c>
+      <c r="F6" s="59">
+        <v>53.1</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>2559</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>2560</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="28" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E7" s="39">
+        <v>-31</v>
+      </c>
+      <c r="F7" s="59">
+        <v>50.27</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>2545</v>
+      </c>
+      <c r="H7" s="62" t="s">
+        <v>2552</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>2598</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E8" s="39">
+        <v>-30.8</v>
+      </c>
+      <c r="F8" s="59">
+        <v>49.6</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>2593</v>
+      </c>
+      <c r="H8" s="63" t="s">
+        <v>2594</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="29" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E9" s="39">
+        <v>-30.5</v>
+      </c>
+      <c r="F9" s="59">
+        <v>50.866700000000002</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>2565</v>
+      </c>
+      <c r="H9" s="62" t="s">
+        <v>2566</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="28" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D10" s="61" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E10" s="39">
+        <v>-29.4</v>
+      </c>
+      <c r="F10" s="59">
+        <v>53.083100000000002</v>
+      </c>
+      <c r="G10" s="60" t="s">
+        <v>2550</v>
+      </c>
+      <c r="H10" s="62" t="s">
+        <v>2553</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="12" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E11" s="39">
+        <v>-27.9</v>
+      </c>
+      <c r="F11" s="59">
+        <v>53</v>
+      </c>
+      <c r="G11" s="60" t="s">
+        <v>2591</v>
+      </c>
+      <c r="H11" s="62" t="s">
+        <v>2592</v>
+      </c>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="29" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>2571</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E12" s="39">
+        <v>-27.9</v>
+      </c>
+      <c r="F12" s="59">
+        <v>53.9</v>
+      </c>
+      <c r="G12" s="60" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>2573</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E13" s="39">
+        <v>-27.3</v>
+      </c>
+      <c r="F13" s="59">
+        <v>50</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>2547</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>2555</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="12" t="s">
         <v>2481</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>2483</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="46" t="s">
+      <c r="B14" s="10" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E14" s="39">
+        <v>-26.4</v>
+      </c>
+      <c r="F14" s="59">
+        <v>43</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>2596</v>
+      </c>
+      <c r="H14" s="62" t="s">
+        <v>2597</v>
+      </c>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E15" s="39">
+        <v>-26.4</v>
+      </c>
+      <c r="F15" s="59">
+        <v>53.616700000000002</v>
+      </c>
+      <c r="G15" s="60" t="s">
+        <v>2562</v>
+      </c>
+      <c r="H15" s="62" t="s">
+        <v>2563</v>
+      </c>
+      <c r="I15" s="27" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E16" s="39">
+        <v>-21.9</v>
+      </c>
+      <c r="F16" s="59">
+        <v>42.4</v>
+      </c>
+      <c r="G16" s="60" t="s">
+        <v>2617</v>
+      </c>
+      <c r="H16" s="62" t="s">
+        <v>2618</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>2607</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E17" s="39">
+        <v>-17.7</v>
+      </c>
+      <c r="F17" s="59">
+        <v>43.7</v>
+      </c>
+      <c r="G17" s="60" t="s">
+        <v>2611</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>2608</v>
+      </c>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="28"/>
+      <c r="B18" s="14" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E18" s="39">
+        <v>-17</v>
+      </c>
+      <c r="F18" s="59">
+        <v>41.8</v>
+      </c>
+      <c r="G18" s="60" t="s">
+        <v>2575</v>
+      </c>
+      <c r="H18" s="62" t="s">
+        <v>2576</v>
+      </c>
+      <c r="I18" s="27" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E19" s="39">
+        <v>-16.8</v>
+      </c>
+      <c r="F19" s="59">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="G19" s="60" t="s">
+        <v>2603</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>2554</v>
+      </c>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E20" s="39">
+        <v>-16.5</v>
+      </c>
+      <c r="F20" s="59">
+        <v>42.7</v>
+      </c>
+      <c r="G20" s="60" t="s">
+        <v>2614</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>2615</v>
+      </c>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>2609</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E21" s="39">
+        <v>-14</v>
+      </c>
+      <c r="F21" s="59">
+        <v>40</v>
+      </c>
+      <c r="G21" s="60" t="s">
+        <v>2610</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>2612</v>
+      </c>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E22" s="39">
+        <v>-13.6</v>
+      </c>
+      <c r="F22" s="59">
+        <v>32.4</v>
+      </c>
+      <c r="G22" s="60" t="s">
+        <v>2605</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>2606</v>
+      </c>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D23" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E23" s="39">
+        <v>-12</v>
+      </c>
+      <c r="F23" s="59">
+        <v>41.8</v>
+      </c>
+      <c r="G23" s="60" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>2624</v>
+      </c>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="12" t="s">
+        <v>782</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E24" s="39">
+        <v>-11.5</v>
+      </c>
+      <c r="F24" s="59">
+        <v>33</v>
+      </c>
+      <c r="G24" s="60" t="s">
+        <v>2620</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>2621</v>
+      </c>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E25" s="39">
+        <v>-8.5</v>
+      </c>
+      <c r="F25" s="59">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="G25" s="60" t="s">
+        <v>2630</v>
+      </c>
+      <c r="H25" s="62" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="26" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>2632</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E26" s="39">
+        <v>-8.5</v>
+      </c>
+      <c r="F26" s="59">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="G26" s="60" t="s">
+        <v>2628</v>
+      </c>
+      <c r="H26" s="62" t="s">
+        <v>2629</v>
+      </c>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>2625</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E27" s="39">
+        <v>-8.4</v>
+      </c>
+      <c r="F27" s="59">
+        <v>36.9</v>
+      </c>
+      <c r="G27" s="60" t="s">
+        <v>2626</v>
+      </c>
+      <c r="H27" s="62" t="s">
+        <v>2627</v>
+      </c>
+      <c r="I27" s="11"/>
+    </row>
+    <row r="28" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="28" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>2509</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D28" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E28" s="39">
+        <v>-7</v>
+      </c>
+      <c r="F28" s="59">
+        <v>43.8</v>
+      </c>
+      <c r="G28" s="60" t="s">
+        <v>2578</v>
+      </c>
+      <c r="H28" s="62" t="s">
+        <v>2577</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="12" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>2637</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E29" s="39">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="F29" s="59">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="G29" s="60" t="s">
+        <v>2638</v>
+      </c>
+      <c r="H29" s="62" t="s">
+        <v>2639</v>
+      </c>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="28"/>
+      <c r="B30" s="14" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E30" s="39">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="F30" s="59">
+        <v>37.9</v>
+      </c>
+      <c r="G30" s="60" t="s">
+        <v>2580</v>
+      </c>
+      <c r="H30" s="62" t="s">
+        <v>2579</v>
+      </c>
+      <c r="I30" s="27" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="12" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E31" s="39">
+        <v>-3.1</v>
+      </c>
+      <c r="F31" s="59">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="G31" s="60" t="s">
+        <v>2635</v>
+      </c>
+      <c r="H31" s="62" t="s">
+        <v>2636</v>
+      </c>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="12" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D32" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E32" s="39">
+        <v>-2</v>
+      </c>
+      <c r="F32" s="59">
+        <v>27.9</v>
+      </c>
+      <c r="G32" s="60" t="s">
+        <v>2641</v>
+      </c>
+      <c r="H32" s="62" t="s">
+        <v>2642</v>
+      </c>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D33" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E33" s="39">
+        <v>-1.8</v>
+      </c>
+      <c r="F33" s="59">
+        <v>36.1</v>
+      </c>
+      <c r="G33" s="60" t="s">
+        <v>2649</v>
+      </c>
+      <c r="H33" s="62" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="12" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>2652</v>
+      </c>
+      <c r="C34" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D34" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E34" s="39">
+        <v>0.3</v>
+      </c>
+      <c r="F34" s="59">
+        <v>34.9</v>
+      </c>
+      <c r="G34" s="60" t="s">
+        <v>2638</v>
+      </c>
+      <c r="H34" s="62" t="s">
+        <v>2653</v>
+      </c>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="12" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>2646</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D35" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E35" s="39">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="59">
+        <v>34.5</v>
+      </c>
+      <c r="G35" s="60" t="s">
+        <v>2647</v>
+      </c>
+      <c r="H35" s="62" t="s">
+        <v>2648</v>
+      </c>
+      <c r="I35" s="11"/>
+    </row>
+    <row r="36" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="12" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C36" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D36" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E36" s="39">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F36" s="59">
+        <v>31.8</v>
+      </c>
+      <c r="G36" s="60" t="s">
+        <v>2657</v>
+      </c>
+      <c r="H36" s="62" t="s">
+        <v>2658</v>
+      </c>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="12" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C37" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D37" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E37" s="39">
+        <v>1.9</v>
+      </c>
+      <c r="F37" s="59">
+        <v>27.1</v>
+      </c>
+      <c r="G37" s="60" t="s">
+        <v>2673</v>
+      </c>
+      <c r="H37" s="62" t="s">
+        <v>2674</v>
+      </c>
+      <c r="I37" s="11"/>
+    </row>
+    <row r="38" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="12" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C38" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D38" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E38" s="39">
+        <v>2.9</v>
+      </c>
+      <c r="F38" s="59">
+        <v>32</v>
+      </c>
+      <c r="G38" s="60" t="s">
+        <v>2644</v>
+      </c>
+      <c r="H38" s="62" t="s">
+        <v>2645</v>
+      </c>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="39" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="12" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C39" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D39" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E39" s="39">
+        <v>3.8</v>
+      </c>
+      <c r="F39" s="59">
+        <v>31</v>
+      </c>
+      <c r="G39" s="60" t="s">
+        <v>2655</v>
+      </c>
+      <c r="H39" s="62" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I39" s="11"/>
+    </row>
+    <row r="40" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="12" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>2675</v>
+      </c>
+      <c r="C40" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D40" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E40" s="39">
+        <v>3.9</v>
+      </c>
+      <c r="F40" s="59">
+        <v>31.7</v>
+      </c>
+      <c r="G40" s="60" t="s">
+        <v>2676</v>
+      </c>
+      <c r="H40" s="62" t="s">
+        <v>2677</v>
+      </c>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="12" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>2666</v>
+      </c>
+      <c r="C41" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D41" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E41" s="39">
+        <v>4.5</v>
+      </c>
+      <c r="F41" s="59">
+        <v>29.5</v>
+      </c>
+      <c r="G41" s="60" t="s">
+        <v>2667</v>
+      </c>
+      <c r="H41" s="62" t="s">
+        <v>2668</v>
+      </c>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C42" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D42" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E42" s="39">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F42" s="59">
+        <v>29.7</v>
+      </c>
+      <c r="G42" s="60" t="s">
+        <v>2662</v>
+      </c>
+      <c r="H42" s="62" t="s">
+        <v>2660</v>
+      </c>
+      <c r="I42" s="11"/>
+    </row>
+    <row r="43" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="12" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>2669</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D43" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E43" s="39">
+        <v>5.7</v>
+      </c>
+      <c r="F43" s="59">
+        <v>27.5</v>
+      </c>
+      <c r="G43" s="60" t="s">
+        <v>2670</v>
+      </c>
+      <c r="H43" s="62" t="s">
+        <v>2671</v>
+      </c>
+      <c r="I43" s="11"/>
+    </row>
+    <row r="44" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="12" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>2678</v>
+      </c>
+      <c r="C44" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D44" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E44" s="39">
+        <v>6</v>
+      </c>
+      <c r="F44" s="59">
+        <v>26</v>
+      </c>
+      <c r="G44" s="60" t="s">
+        <v>2679</v>
+      </c>
+      <c r="H44" s="62" t="s">
+        <v>2680</v>
+      </c>
+      <c r="I44" s="11"/>
+    </row>
+    <row r="45" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="12" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C45" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D45" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E45" s="39">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F45" s="59">
+        <v>24.6</v>
+      </c>
+      <c r="G45" s="60" t="s">
+        <v>2589</v>
+      </c>
+      <c r="H45" s="62" t="s">
+        <v>2682</v>
+      </c>
+      <c r="I45" s="11"/>
+    </row>
+    <row r="46" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="12" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>2663</v>
+      </c>
+      <c r="C46" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D46" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E46" s="39">
+        <v>12</v>
+      </c>
+      <c r="F46" s="59">
+        <v>25.2</v>
+      </c>
+      <c r="G46" s="60" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H46" s="62" t="s">
+        <v>2665</v>
+      </c>
+      <c r="I46" s="11"/>
+    </row>
+    <row r="47" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="12"/>
+      <c r="B47" s="10" t="s">
         <v>2488</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="C47" s="46" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D47" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E47" s="39">
+        <v>15.2</v>
+      </c>
+      <c r="F47" s="59">
+        <v>22.2</v>
+      </c>
+      <c r="G47" s="60" t="s">
+        <v>2583</v>
+      </c>
+      <c r="H47" s="62" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I47" s="11"/>
+    </row>
+    <row r="48" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="12"/>
+      <c r="B48" s="10" t="s">
         <v>2489</v>
       </c>
-      <c r="C3" s="15">
-        <v>-53</v>
-      </c>
-      <c r="D3" s="12">
-        <v>44948</v>
-      </c>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="46" t="s">
-        <v>2490</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>2491</v>
-      </c>
-      <c r="C4" s="16">
-        <v>-52.4</v>
-      </c>
-      <c r="D4" s="12">
-        <v>44948</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>2503</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>2482</v>
-      </c>
-      <c r="C5" s="16">
-        <v>-52.3</v>
-      </c>
-      <c r="D5" s="12">
-        <v>25247</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>2484</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="54"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="18">
-        <v>-50.3</v>
-      </c>
-      <c r="D6" s="12">
-        <v>44948</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>2485</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="46" t="s">
-        <v>2486</v>
-      </c>
-      <c r="B7" s="45" t="s">
-        <v>2487</v>
-      </c>
-      <c r="C7" s="16">
-        <v>-52.3</v>
-      </c>
-      <c r="D7" s="12">
-        <v>45340</v>
-      </c>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="46" t="s">
-        <v>2488</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>2510</v>
-      </c>
-      <c r="C8" s="17">
-        <v>-51.8</v>
-      </c>
-      <c r="D8" s="12">
-        <v>44948</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>2503</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="46" t="s">
-        <v>2490</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>2492</v>
-      </c>
-      <c r="C9" s="17">
-        <v>-51.8</v>
-      </c>
-      <c r="D9" s="12">
-        <v>44948</v>
-      </c>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="10" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>2502</v>
-      </c>
-      <c r="C10" s="17">
-        <v>-51.5</v>
-      </c>
-      <c r="D10" s="12">
-        <v>21936</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>2504</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="46" t="s">
-        <v>2490</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>2509</v>
-      </c>
-      <c r="C11" s="17">
-        <v>-51.2</v>
-      </c>
-      <c r="D11" s="12">
-        <v>44949</v>
-      </c>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="46" t="s">
-        <v>2488</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>2493</v>
-      </c>
-      <c r="C12" s="18">
-        <v>-50.8</v>
-      </c>
-      <c r="D12" s="12">
-        <v>44948</v>
-      </c>
-      <c r="E12" s="14"/>
-    </row>
-    <row r="13" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="19">
-        <v>-50</v>
-      </c>
-      <c r="D13" s="12">
-        <v>24160</v>
-      </c>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="20">
-        <v>-49.8</v>
-      </c>
-      <c r="D14" s="12">
-        <v>44947</v>
-      </c>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="20">
-        <v>-49.7</v>
-      </c>
-      <c r="D15" s="12">
-        <v>25230</v>
-      </c>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="16" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="46" t="s">
-        <v>2506</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>2507</v>
-      </c>
-      <c r="C16" s="20">
-        <v>-49.7</v>
-      </c>
-      <c r="D16" s="12">
-        <v>42014</v>
-      </c>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="C17" s="20">
-        <v>-49.6</v>
-      </c>
-      <c r="D17" s="12">
-        <v>21938</v>
-      </c>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="20">
-        <v>-49.6</v>
-      </c>
-      <c r="D18" s="12">
-        <v>40553</v>
-      </c>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B19" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="C19" s="21">
-        <v>-48.5</v>
-      </c>
-      <c r="D19" s="12">
-        <v>18631</v>
-      </c>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="21">
-        <v>-48.3</v>
-      </c>
-      <c r="D20" s="12">
-        <v>44948</v>
-      </c>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="21">
-        <v>-48.2</v>
-      </c>
-      <c r="D21" s="12">
-        <v>20474</v>
-      </c>
-      <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="C22" s="21">
-        <v>-48.1</v>
-      </c>
-      <c r="D22" s="12">
-        <v>28492</v>
-      </c>
-      <c r="E22" s="14"/>
-    </row>
-    <row r="23" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="21">
-        <v>-48.1</v>
-      </c>
-      <c r="D23" s="12">
-        <v>29233</v>
-      </c>
-      <c r="E23" s="14"/>
-    </row>
-    <row r="24" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="22">
-        <v>-48</v>
-      </c>
-      <c r="D24" s="12">
-        <v>21938</v>
-      </c>
-      <c r="E24" s="14"/>
-    </row>
-    <row r="25" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="22">
-        <v>-47.9</v>
-      </c>
-      <c r="D25" s="12">
-        <v>29233</v>
-      </c>
-      <c r="E25" s="14"/>
-    </row>
-    <row r="26" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="22">
-        <v>-47.9</v>
-      </c>
-      <c r="D26" s="12">
-        <v>44947</v>
-      </c>
-      <c r="E26" s="14"/>
-    </row>
-    <row r="27" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="22">
-        <v>-47.7</v>
-      </c>
-      <c r="D27" s="12">
-        <v>25570</v>
-      </c>
-      <c r="E27" s="14"/>
-    </row>
-    <row r="28" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="22">
-        <v>-47.3</v>
-      </c>
-      <c r="D28" s="12">
-        <v>18632</v>
-      </c>
-      <c r="E28" s="14"/>
-    </row>
-    <row r="29" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B29" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="23">
-        <v>-46.8</v>
-      </c>
-      <c r="D29" s="12">
-        <v>42391</v>
-      </c>
-      <c r="E29" s="14"/>
-    </row>
-    <row r="30" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B30" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="23">
-        <v>-46.7</v>
-      </c>
-      <c r="D30" s="12">
-        <v>25583</v>
-      </c>
-      <c r="E30" s="14"/>
-    </row>
-    <row r="31" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B31" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="C31" s="23">
-        <v>-46.5</v>
-      </c>
-      <c r="D31" s="12">
-        <v>31787</v>
-      </c>
-      <c r="E31" s="14"/>
-    </row>
-    <row r="32" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="46" t="s">
-        <v>370</v>
-      </c>
-      <c r="B32" s="45" t="s">
-        <v>371</v>
-      </c>
-      <c r="C32" s="23">
-        <v>-46.4</v>
-      </c>
-      <c r="D32" s="12">
-        <v>24114</v>
-      </c>
-      <c r="E32" s="14"/>
-    </row>
-    <row r="33" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B33" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="C33" s="24">
-        <v>-46</v>
-      </c>
-      <c r="D33" s="12">
-        <v>24125</v>
-      </c>
-      <c r="E33" s="14"/>
-    </row>
-    <row r="34" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="B34" s="45" t="s">
-        <v>320</v>
-      </c>
-      <c r="C34" s="24">
-        <v>-45.9</v>
-      </c>
-      <c r="D34" s="12">
-        <v>42014</v>
-      </c>
-      <c r="E34" s="14"/>
-    </row>
-    <row r="35" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="B35" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="C35" s="24">
-        <v>-45.7</v>
-      </c>
-      <c r="D35" s="12">
-        <v>24126</v>
-      </c>
-      <c r="E35" s="14"/>
-    </row>
-    <row r="36" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="24">
-        <v>-45.4</v>
-      </c>
-      <c r="D36" s="12">
-        <v>29233</v>
-      </c>
-      <c r="E36" s="14"/>
-    </row>
-    <row r="37" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="B37" s="45" t="s">
-        <v>321</v>
-      </c>
-      <c r="C37" s="24">
-        <v>-45.2</v>
-      </c>
-      <c r="D37" s="12">
-        <v>31418</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>2503</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="46" t="s">
-        <v>411</v>
-      </c>
-      <c r="B38" s="45" t="s">
-        <v>412</v>
-      </c>
-      <c r="C38" s="25">
-        <v>-45</v>
-      </c>
-      <c r="D38" s="12">
-        <v>25572</v>
-      </c>
-      <c r="E38" s="14"/>
-    </row>
-    <row r="39" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="25">
-        <v>-45</v>
-      </c>
-      <c r="D39" s="12">
-        <v>40556</v>
-      </c>
-      <c r="E39" s="14"/>
-    </row>
-    <row r="40" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="46" t="s">
-        <v>466</v>
-      </c>
-      <c r="B40" s="45" t="s">
-        <v>467</v>
-      </c>
-      <c r="C40" s="25">
-        <v>-44.8</v>
-      </c>
-      <c r="D40" s="12">
-        <v>21200</v>
-      </c>
-      <c r="E40" s="14"/>
-    </row>
-    <row r="41" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="46" t="s">
-        <v>576</v>
-      </c>
-      <c r="B41" s="45" t="s">
-        <v>577</v>
-      </c>
-      <c r="C41" s="26">
-        <v>-43.4</v>
-      </c>
-      <c r="D41" s="12">
-        <v>36904</v>
-      </c>
-      <c r="E41" s="14"/>
-    </row>
-    <row r="42" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="46" t="s">
-        <v>639</v>
-      </c>
-      <c r="B42" s="45" t="s">
-        <v>640</v>
-      </c>
-      <c r="C42" s="27">
-        <v>-39.9</v>
-      </c>
-      <c r="D42" s="12">
-        <v>36557</v>
-      </c>
-      <c r="E42" s="14"/>
-    </row>
-    <row r="43" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="46" t="s">
-        <v>782</v>
-      </c>
-      <c r="B43" s="45" t="s">
-        <v>783</v>
-      </c>
-      <c r="C43" s="28">
-        <v>-37.799999999999997</v>
-      </c>
-      <c r="D43" s="12">
-        <v>35062</v>
-      </c>
-      <c r="E43" s="14"/>
-    </row>
-    <row r="44" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="46" t="s">
-        <v>942</v>
-      </c>
-      <c r="B44" s="45" t="s">
-        <v>943</v>
-      </c>
-      <c r="C44" s="28">
-        <v>-37.1</v>
-      </c>
-      <c r="D44" s="12">
-        <v>37615</v>
-      </c>
-      <c r="E44" s="14"/>
-    </row>
-    <row r="45" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="46" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B45" s="45" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C45" s="29">
-        <v>-33.200000000000003</v>
-      </c>
-      <c r="D45" s="12">
-        <v>24816</v>
-      </c>
-      <c r="E45" s="14"/>
-    </row>
-    <row r="46" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="46" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B46" s="45" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C46" s="29">
-        <v>-33.200000000000003</v>
-      </c>
-      <c r="D46" s="12">
-        <v>29250</v>
-      </c>
-      <c r="E46" s="14"/>
-    </row>
-    <row r="47" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="46" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B47" s="45" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C47" s="30">
-        <v>-32.700000000000003</v>
-      </c>
-      <c r="D47" s="12">
-        <v>20086</v>
-      </c>
-      <c r="E47" s="14"/>
-    </row>
-    <row r="48" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="46" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B48" s="45" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C48" s="31">
-        <v>-27.5</v>
-      </c>
-      <c r="D48" s="12">
-        <v>21200</v>
-      </c>
-      <c r="E48" s="14"/>
-    </row>
-    <row r="49" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="46" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B49" s="45" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C49" s="31">
-        <v>-27.4</v>
-      </c>
-      <c r="D49" s="12">
-        <v>24160</v>
-      </c>
-      <c r="E49" s="14"/>
-    </row>
-    <row r="50" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="46" t="s">
-        <v>1314</v>
-      </c>
-      <c r="B50" s="45" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C50" s="31">
-        <v>-27.4</v>
-      </c>
-      <c r="D50" s="12">
-        <v>30312</v>
-      </c>
-      <c r="E50" s="14"/>
-    </row>
-    <row r="51" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="46" t="s">
-        <v>1443</v>
-      </c>
-      <c r="B51" s="45" t="s">
-        <v>1444</v>
-      </c>
-      <c r="C51" s="32">
-        <v>-25.8</v>
-      </c>
-      <c r="D51" s="12">
-        <v>20813</v>
-      </c>
-      <c r="E51" s="14"/>
-    </row>
-    <row r="52" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="46" t="s">
-        <v>1479</v>
-      </c>
-      <c r="B52" s="45" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C52" s="33">
-        <v>-24.3</v>
-      </c>
-      <c r="D52" s="12">
-        <v>25240</v>
-      </c>
-      <c r="E52" s="14"/>
-    </row>
-    <row r="53" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="B53" s="45" t="s">
-        <v>1561</v>
-      </c>
-      <c r="C53" s="34">
-        <v>-23.6</v>
-      </c>
-      <c r="D53" s="12">
-        <v>28120</v>
-      </c>
-      <c r="E53" s="14"/>
-    </row>
-    <row r="54" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="46" t="s">
-        <v>1681</v>
-      </c>
-      <c r="B54" s="45" t="s">
-        <v>1682</v>
-      </c>
-      <c r="C54" s="34">
-        <v>-23.4</v>
-      </c>
-      <c r="D54" s="12">
-        <v>25239</v>
-      </c>
-      <c r="E54" s="14"/>
-    </row>
-    <row r="55" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="46" t="s">
-        <v>1754</v>
-      </c>
-      <c r="B55" s="45" t="s">
-        <v>1755</v>
-      </c>
-      <c r="C55" s="35">
-        <v>-19.7</v>
-      </c>
-      <c r="D55" s="12">
-        <v>28155</v>
-      </c>
-      <c r="E55" s="14"/>
-    </row>
-    <row r="56" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="46" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B56" s="45" t="s">
-        <v>1842</v>
-      </c>
-      <c r="C56" s="36">
-        <v>-18.899999999999999</v>
-      </c>
-      <c r="D56" s="12">
-        <v>25240</v>
-      </c>
-      <c r="E56" s="14"/>
-    </row>
-    <row r="57" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="46" t="s">
-        <v>2494</v>
-      </c>
-      <c r="B57" s="45" t="s">
-        <v>2495</v>
-      </c>
-      <c r="C57" s="36">
-        <v>-18.399999999999999</v>
-      </c>
-      <c r="D57" s="12">
-        <v>25599</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="46" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B58" s="45" t="s">
-        <v>1938</v>
-      </c>
-      <c r="C58" s="36">
-        <v>-18.100000000000001</v>
-      </c>
-      <c r="D58" s="12">
-        <v>25234</v>
-      </c>
-      <c r="E58" s="14"/>
-    </row>
-    <row r="59" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="46" t="s">
-        <v>2036</v>
-      </c>
-      <c r="B59" s="45" t="s">
-        <v>2037</v>
-      </c>
-      <c r="C59" s="37">
-        <v>-17.399999999999999</v>
-      </c>
-      <c r="D59" s="12">
-        <v>28130</v>
-      </c>
-      <c r="E59" s="14"/>
-    </row>
-    <row r="60" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="46" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B60" s="45" t="s">
-        <v>2113</v>
-      </c>
-      <c r="C60" s="38">
-        <v>-15.6</v>
-      </c>
-      <c r="D60" s="12">
-        <v>42394</v>
-      </c>
-      <c r="E60" s="14"/>
-    </row>
-    <row r="61" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="46" t="s">
-        <v>2183</v>
-      </c>
-      <c r="B61" s="45" t="s">
-        <v>2184</v>
-      </c>
-      <c r="C61" s="38">
-        <v>-15.3</v>
-      </c>
-      <c r="D61" s="12">
-        <v>28165</v>
-      </c>
-      <c r="E61" s="14"/>
-    </row>
-    <row r="62" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="46" t="s">
-        <v>2267</v>
-      </c>
-      <c r="B62" s="45" t="s">
-        <v>2268</v>
-      </c>
-      <c r="C62" s="39">
-        <v>-11</v>
-      </c>
-      <c r="D62" s="12">
-        <v>28156</v>
-      </c>
-      <c r="E62" s="14"/>
-    </row>
-    <row r="63" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="46" t="s">
-        <v>2280</v>
-      </c>
-      <c r="B63" s="45" t="s">
-        <v>2281</v>
-      </c>
-      <c r="C63" s="40">
-        <v>-8.4</v>
-      </c>
-      <c r="D63" s="12">
-        <v>23026</v>
-      </c>
-      <c r="E63" s="14"/>
-    </row>
-    <row r="64" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="46" t="s">
-        <v>2372</v>
-      </c>
-      <c r="B64" s="45" t="s">
-        <v>2373</v>
-      </c>
-      <c r="C64" s="41">
-        <v>-7.3</v>
-      </c>
-      <c r="D64" s="12">
-        <v>20101</v>
-      </c>
-      <c r="E64" s="14"/>
-    </row>
-    <row r="65" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="46" t="s">
-        <v>2498</v>
-      </c>
-      <c r="B65" s="45" t="s">
-        <v>2499</v>
-      </c>
-      <c r="C65" s="42">
-        <v>-6</v>
-      </c>
-      <c r="D65" s="12">
-        <v>42393</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="46" t="s">
+      <c r="C48" s="47" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D48" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E48" s="39">
+        <v>16.8</v>
+      </c>
+      <c r="F48" s="59">
+        <v>22.3</v>
+      </c>
+      <c r="G48" s="60" t="s">
+        <v>2585</v>
+      </c>
+      <c r="H48" s="62" t="s">
+        <v>2586</v>
+      </c>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="12" t="s">
         <v>2459</v>
       </c>
-      <c r="B66" s="45" t="s">
-        <v>2460</v>
-      </c>
-      <c r="C66" s="43">
-        <v>-1.4</v>
-      </c>
-      <c r="D66" s="12">
-        <v>23026</v>
-      </c>
-      <c r="E66" s="14"/>
-    </row>
-    <row r="67" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A67" s="46" t="s">
-        <v>2497</v>
-      </c>
-      <c r="B67" s="45" t="s">
-        <v>2496</v>
-      </c>
-      <c r="C67" s="44">
-        <v>1.6</v>
-      </c>
-      <c r="D67" s="12">
-        <v>42393</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>2501</v>
-      </c>
+      <c r="B49" s="10" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C49" s="57" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D49" s="61" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E49" s="39">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F49" s="59">
+        <v>19</v>
+      </c>
+      <c r="G49" s="60" t="s">
+        <v>2589</v>
+      </c>
+      <c r="H49" s="62" t="s">
+        <v>2590</v>
+      </c>
+      <c r="I49" s="11"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E67">
-    <sortCondition ref="C3:C67"/>
-    <sortCondition ref="D3:D67"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I49">
+    <sortCondition ref="E3:E49"/>
+    <sortCondition ref="F3:F49"/>
   </sortState>
-  <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A5:A6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
